--- a/results/04-2026/04.30/beta/inputs-04-2026.xlsx
+++ b/results/04-2026/04.30/beta/inputs-04-2026.xlsx
@@ -4759,13 +4759,13 @@
         <v>3463.7487875286</v>
       </c>
       <c r="Q27" t="n">
-        <v>5117.7343736848</v>
+        <v>5047.7343736848</v>
       </c>
       <c r="R27" t="n">
         <v>2626.36869158331</v>
       </c>
       <c r="S27" t="n">
-        <v>432.67747940975</v>
+        <v>357.67747940975</v>
       </c>
       <c r="T27" t="n">
         <v>156.945251003532</v>
@@ -4816,13 +4816,13 @@
         <v>348.008366328366</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-2965.37812484218</v>
+        <v>-2956.97812484218</v>
       </c>
       <c r="AK27" t="n">
         <v>-1519.05824299</v>
       </c>
       <c r="AL27" t="n">
-        <v>-177.366618484671</v>
+        <v>-174.866618484671</v>
       </c>
       <c r="AM27" t="n">
         <v>-70.2697062192393</v>
@@ -4917,13 +4917,13 @@
         <v>3497.25612764809</v>
       </c>
       <c r="Q28" t="n">
-        <v>5156.07541767194</v>
+        <v>5085.41968920096</v>
       </c>
       <c r="R28" t="n">
         <v>2656.13677457201</v>
       </c>
       <c r="S28" t="n">
-        <v>420.676259283967</v>
+        <v>347.756542063329</v>
       </c>
       <c r="T28" t="n">
         <v>164.885835526837</v>
@@ -4974,13 +4974,13 @@
         <v>353.222696367226</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-3006.53517496281</v>
+        <v>-2989.65648754629</v>
       </c>
       <c r="AK28" t="n">
         <v>-1538.22665593864</v>
       </c>
       <c r="AL28" t="n">
-        <v>-177.109160460803</v>
+        <v>-172.178503220115</v>
       </c>
       <c r="AM28" t="n">
         <v>-70.6576510961968</v>
@@ -5075,13 +5075,13 @@
         <v>3528.12789542346</v>
       </c>
       <c r="Q29" t="n">
-        <v>5190.38689030448</v>
+        <v>5119.06929079356</v>
       </c>
       <c r="R29" t="n">
         <v>2684.09748115581</v>
       </c>
       <c r="S29" t="n">
-        <v>439.007918245637</v>
+        <v>443.110782785133</v>
       </c>
       <c r="T29" t="n">
         <v>162.643016309613</v>
@@ -5132,13 +5132,13 @@
         <v>355.865936362206</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-3046.89953937826</v>
+        <v>-3025.66274002043</v>
       </c>
       <c r="AK29" t="n">
         <v>-1556.54023218234</v>
       </c>
       <c r="AL29" t="n">
-        <v>-176.986091068991</v>
+        <v>-172.192195979619</v>
       </c>
       <c r="AM29" t="n">
         <v>-70.9432727516778</v>
@@ -5233,13 +5233,13 @@
         <v>3560.36271193125</v>
       </c>
       <c r="Q30" t="n">
-        <v>5447.69456827922</v>
+        <v>5375.70889761857</v>
       </c>
       <c r="R30" t="n">
         <v>2709.61779256644</v>
       </c>
       <c r="S30" t="n">
-        <v>443.111839208704</v>
+        <v>447.253058026317</v>
       </c>
       <c r="T30" t="n">
         <v>143.140105616203</v>
@@ -5290,13 +5290,13 @@
         <v>356.859779384814</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-3108.60436251145</v>
+        <v>-3082.9686263826</v>
       </c>
       <c r="AK30" t="n">
         <v>-1574.72016081599</v>
       </c>
       <c r="AL30" t="n">
-        <v>-176.013152375948</v>
+        <v>-171.35729791383</v>
       </c>
       <c r="AM30" t="n">
         <v>-71.1937227740491</v>
@@ -5391,13 +5391,13 @@
         <v>3592.51954751041</v>
       </c>
       <c r="Q31" t="n">
-        <v>5483.42963386668</v>
+        <v>5410.76963386668</v>
       </c>
       <c r="R31" t="n">
         <v>2735.18355114505</v>
       </c>
       <c r="S31" t="n">
-        <v>447.254124325517</v>
+        <v>451.434055963587</v>
       </c>
       <c r="T31" t="n">
         <v>115.322937925207</v>
@@ -5448,13 +5448,13 @@
         <v>358.739093739241</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-3159.66870515718</v>
+        <v>-3129.59282499899</v>
       </c>
       <c r="AK31" t="n">
         <v>-1592.46633808405</v>
       </c>
       <c r="AL31" t="n">
-        <v>-174.411623186798</v>
+        <v>-169.895099779283</v>
       </c>
       <c r="AM31" t="n">
         <v>-71.5336735570469</v>
@@ -5549,13 +5549,13 @@
         <v>3623.5322358997</v>
       </c>
       <c r="Q32" t="n">
-        <v>5519.44070620309</v>
+        <v>5446.10006005022</v>
       </c>
       <c r="R32" t="n">
         <v>2761.80377090598</v>
       </c>
       <c r="S32" t="n">
-        <v>451.435132230733</v>
+        <v>455.654138583314</v>
       </c>
       <c r="T32" t="n">
         <v>85.0823596752584</v>
@@ -5606,13 +5606,13 @@
         <v>360.222346635286</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-3190.8019158048</v>
+        <v>-3156.2442983479</v>
       </c>
       <c r="AK32" t="n">
         <v>-1609.88972303878</v>
       </c>
       <c r="AL32" t="n">
-        <v>-173.106127594489</v>
+        <v>-168.73023773206</v>
       </c>
       <c r="AM32" t="n">
         <v>-71.8826222818791</v>
@@ -5707,13 +5707,13 @@
         <v>3654.41530888475</v>
       </c>
       <c r="Q33" t="n">
-        <v>5554.96361371836</v>
+        <v>5480.93594542602</v>
       </c>
       <c r="R33" t="n">
         <v>2788.75455279793</v>
       </c>
       <c r="S33" t="n">
-        <v>455.65522491159</v>
+        <v>459.913671255784</v>
       </c>
       <c r="T33" t="n">
         <v>50.6890505411461</v>
@@ -5764,13 +5764,13 @@
         <v>367.007979818939</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-3218.617771419</v>
+        <v>-3179.53643376702</v>
       </c>
       <c r="AK33" t="n">
         <v>-1626.31325630583</v>
       </c>
       <c r="AL33" t="n">
-        <v>-171.341301758209</v>
+        <v>-167.107360107253</v>
       </c>
       <c r="AM33" t="n">
         <v>-72.1367489038031</v>
@@ -5865,13 +5865,13 @@
         <v>3685.16965313856</v>
       </c>
       <c r="Q34" t="n">
-        <v>5638.71752992768</v>
+        <v>5563.99640378192</v>
       </c>
       <c r="R34" t="n">
         <v>2816.33443957647</v>
       </c>
       <c r="S34" t="n">
-        <v>459.914767739242</v>
+        <v>464.213022766824</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -5922,13 +5922,13 @@
         <v>375.061936771887</v>
       </c>
       <c r="AJ34" t="n">
-        <v>-3258.12743263814</v>
+        <v>-3214.47999861784</v>
       </c>
       <c r="AK34" t="n">
         <v>-1643.00316280064</v>
       </c>
       <c r="AL34" t="n">
-        <v>-171.031794016184</v>
+        <v>-166.941127532814</v>
       </c>
       <c r="AM34" t="n">
         <v>-72.041206263982</v>

--- a/results/04-2026/04.30/beta/inputs-04-2026.xlsx
+++ b/results/04-2026/04.30/beta/inputs-04-2026.xlsx
@@ -4765,7 +4765,7 @@
         <v>2626.36869158331</v>
       </c>
       <c r="S27" t="n">
-        <v>357.67747940975</v>
+        <v>132.67747940975</v>
       </c>
       <c r="T27" t="n">
         <v>156.945251003532</v>
@@ -4822,7 +4822,7 @@
         <v>-1519.05824299</v>
       </c>
       <c r="AL27" t="n">
-        <v>-174.866618484671</v>
+        <v>-167.366618484671</v>
       </c>
       <c r="AM27" t="n">
         <v>-70.2697062192393</v>
@@ -4923,7 +4923,7 @@
         <v>2656.13677457201</v>
       </c>
       <c r="S28" t="n">
-        <v>347.756542063329</v>
+        <v>128.997390401414</v>
       </c>
       <c r="T28" t="n">
         <v>164.885835526837</v>
@@ -4980,7 +4980,7 @@
         <v>-1538.22665593864</v>
       </c>
       <c r="AL28" t="n">
-        <v>-172.178503220115</v>
+        <v>-157.386531498051</v>
       </c>
       <c r="AM28" t="n">
         <v>-70.6576510961968</v>
@@ -5081,7 +5081,7 @@
         <v>2684.09748115581</v>
       </c>
       <c r="S29" t="n">
-        <v>443.110782785133</v>
+        <v>455.419376403618</v>
       </c>
       <c r="T29" t="n">
         <v>162.643016309613</v>
@@ -5138,7 +5138,7 @@
         <v>-1556.54023218234</v>
       </c>
       <c r="AL29" t="n">
-        <v>-172.192195979619</v>
+        <v>-157.810510711505</v>
       </c>
       <c r="AM29" t="n">
         <v>-70.9432727516778</v>
@@ -5239,7 +5239,7 @@
         <v>2709.61779256644</v>
       </c>
       <c r="S30" t="n">
-        <v>447.253058026317</v>
+        <v>459.676714479156</v>
       </c>
       <c r="T30" t="n">
         <v>143.140105616203</v>
@@ -5296,7 +5296,7 @@
         <v>-1574.72016081599</v>
       </c>
       <c r="AL30" t="n">
-        <v>-171.35729791383</v>
+        <v>-157.389734527477</v>
       </c>
       <c r="AM30" t="n">
         <v>-71.1937227740491</v>
@@ -5397,7 +5397,7 @@
         <v>2735.18355114505</v>
       </c>
       <c r="S31" t="n">
-        <v>451.434055963587</v>
+        <v>463.973850877797</v>
       </c>
       <c r="T31" t="n">
         <v>115.322937925207</v>
@@ -5454,7 +5454,7 @@
         <v>-1592.46633808405</v>
       </c>
       <c r="AL31" t="n">
-        <v>-169.895099779283</v>
+        <v>-156.345529556737</v>
       </c>
       <c r="AM31" t="n">
         <v>-71.5336735570469</v>
@@ -5555,7 +5555,7 @@
         <v>2761.80377090598</v>
       </c>
       <c r="S32" t="n">
-        <v>455.654138583314</v>
+        <v>468.311157641058</v>
       </c>
       <c r="T32" t="n">
         <v>85.0823596752584</v>
@@ -5612,7 +5612,7 @@
         <v>-1609.88972303878</v>
       </c>
       <c r="AL32" t="n">
-        <v>-168.73023773206</v>
+        <v>-155.602568144772</v>
       </c>
       <c r="AM32" t="n">
         <v>-71.8826222818791</v>
@@ -5713,7 +5713,7 @@
         <v>2788.75455279793</v>
       </c>
       <c r="S33" t="n">
-        <v>459.913671255784</v>
+        <v>472.689010288367</v>
       </c>
       <c r="T33" t="n">
         <v>50.6890505411461</v>
@@ -5770,7 +5770,7 @@
         <v>-1626.31325630583</v>
       </c>
       <c r="AL33" t="n">
-        <v>-167.107360107253</v>
+        <v>-154.405535154384</v>
       </c>
       <c r="AM33" t="n">
         <v>-72.1367489038031</v>
@@ -5871,7 +5871,7 @@
         <v>2816.33443957647</v>
       </c>
       <c r="S34" t="n">
-        <v>464.213022766824</v>
+        <v>477.107787849569</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
         <v>-1643.00316280064</v>
       </c>
       <c r="AL34" t="n">
-        <v>-166.941127532814</v>
+        <v>-154.669128082703</v>
       </c>
       <c r="AM34" t="n">
         <v>-72.041206263982</v>
